--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NORTH_CAROLINA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NORTH_CAROLINA_2020.xlsx
@@ -463,7 +463,7 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="7">
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="D26">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="27">
@@ -913,7 +913,7 @@
         <v>2</v>
       </c>
       <c r="D31">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="32">
@@ -1003,7 +1003,7 @@
         <v>2</v>
       </c>
       <c r="D36">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="37">
@@ -1021,7 +1021,7 @@
         <v>2</v>
       </c>
       <c r="D37">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="38">
@@ -1309,7 +1309,7 @@
         <v>2</v>
       </c>
       <c r="D53">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="54">
@@ -1345,7 +1345,7 @@
         <v>2</v>
       </c>
       <c r="D55">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="56">
@@ -1363,7 +1363,7 @@
         <v>2</v>
       </c>
       <c r="D56">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="57">
@@ -1381,7 +1381,7 @@
         <v>2</v>
       </c>
       <c r="D57">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="58">
@@ -1651,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="D72">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="73">
@@ -1723,7 +1723,7 @@
         <v>2</v>
       </c>
       <c r="D76">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="77">
@@ -1993,7 +1993,7 @@
         <v>2</v>
       </c>
       <c r="D91">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="92">
@@ -2047,7 +2047,7 @@
         <v>2</v>
       </c>
       <c r="D94">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="95">
@@ -2155,7 +2155,7 @@
         <v>2</v>
       </c>
       <c r="D100">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="101">
@@ -2263,7 +2263,7 @@
         <v>2</v>
       </c>
       <c r="D106">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="107">
@@ -2335,7 +2335,7 @@
         <v>2</v>
       </c>
       <c r="D110">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="111">
@@ -2454,14 +2454,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="118">
@@ -2659,7 +2659,7 @@
         <v>2</v>
       </c>
       <c r="D128">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="129">
@@ -2695,7 +2695,7 @@
         <v>2</v>
       </c>
       <c r="D130">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="131">
@@ -2749,7 +2749,7 @@
         <v>2</v>
       </c>
       <c r="D133">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="134">
@@ -3073,7 +3073,7 @@
         <v>2</v>
       </c>
       <c r="D151">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="152">
@@ -3433,7 +3433,7 @@
         <v>21</v>
       </c>
       <c r="D171">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="172">
@@ -3685,7 +3685,7 @@
         <v>2</v>
       </c>
       <c r="D185">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="186">
@@ -3721,7 +3721,7 @@
         <v>2</v>
       </c>
       <c r="D187">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="188">
@@ -3739,7 +3739,7 @@
         <v>2</v>
       </c>
       <c r="D188">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="189">
@@ -3757,7 +3757,7 @@
         <v>2</v>
       </c>
       <c r="D189">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="190">
@@ -3919,7 +3919,7 @@
         <v>2</v>
       </c>
       <c r="D198">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="199">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C201">
@@ -4135,7 +4135,7 @@
         <v>2</v>
       </c>
       <c r="D210">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="211">
@@ -4297,7 +4297,7 @@
         <v>2</v>
       </c>
       <c r="D219">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="220">
@@ -4369,7 +4369,7 @@
         <v>2</v>
       </c>
       <c r="D223">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="224">
@@ -4441,7 +4441,7 @@
         <v>2</v>
       </c>
       <c r="D227">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="228">
@@ -4459,7 +4459,7 @@
         <v>2</v>
       </c>
       <c r="D228">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="229">
@@ -4765,7 +4765,7 @@
         <v>2</v>
       </c>
       <c r="D245">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="246">
@@ -4783,7 +4783,7 @@
         <v>21</v>
       </c>
       <c r="D246">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="247">
@@ -4909,7 +4909,7 @@
         <v>2</v>
       </c>
       <c r="D253">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="254">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C254">
@@ -5035,7 +5035,7 @@
         <v>2</v>
       </c>
       <c r="D260">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="261">
@@ -5161,7 +5161,7 @@
         <v>2</v>
       </c>
       <c r="D267">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="268">
@@ -5197,7 +5197,7 @@
         <v>2</v>
       </c>
       <c r="D269">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="270">
@@ -5215,7 +5215,7 @@
         <v>2</v>
       </c>
       <c r="D270">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="271">
@@ -5269,7 +5269,7 @@
         <v>2</v>
       </c>
       <c r="D273">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="274">
@@ -5467,7 +5467,7 @@
         <v>2</v>
       </c>
       <c r="D284">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="285">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C285">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C294">
@@ -5719,7 +5719,7 @@
         <v>211</v>
       </c>
       <c r="D298">
-        <v>0.009725743258815395</v>
+        <v>0.009725743258815396</v>
       </c>
     </row>
     <row r="299">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C304">
@@ -5971,7 +5971,7 @@
         <v>2</v>
       </c>
       <c r="D312">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="313">
@@ -6439,7 +6439,7 @@
         <v>2</v>
       </c>
       <c r="D338">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="339">
@@ -6979,7 +6979,7 @@
         <v>2</v>
       </c>
       <c r="D368">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="369">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C398">
@@ -7609,7 +7609,7 @@
         <v>21</v>
       </c>
       <c r="D403">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="404">
@@ -7789,7 +7789,7 @@
         <v>21</v>
       </c>
       <c r="D413">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="414">
@@ -7807,7 +7807,7 @@
         <v>2</v>
       </c>
       <c r="D414">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="415">
@@ -7825,7 +7825,7 @@
         <v>21</v>
       </c>
       <c r="D415">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="416">
@@ -7879,7 +7879,7 @@
         <v>2</v>
       </c>
       <c r="D418">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="419">
@@ -8041,7 +8041,7 @@
         <v>2</v>
       </c>
       <c r="D427">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="428">
@@ -8239,7 +8239,7 @@
         <v>2</v>
       </c>
       <c r="D438">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="439">
@@ -8545,7 +8545,7 @@
         <v>2</v>
       </c>
       <c r="D455">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="456">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C458">
@@ -8689,7 +8689,7 @@
         <v>2</v>
       </c>
       <c r="D463">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="464">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C464">
@@ -8941,7 +8941,7 @@
         <v>2</v>
       </c>
       <c r="D477">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="478">
@@ -9211,7 +9211,7 @@
         <v>2</v>
       </c>
       <c r="D492">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="493">
@@ -9301,7 +9301,7 @@
         <v>2</v>
       </c>
       <c r="D497">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="498">
@@ -9319,7 +9319,7 @@
         <v>2</v>
       </c>
       <c r="D498">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="499">
@@ -9517,7 +9517,7 @@
         <v>2</v>
       </c>
       <c r="D509">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="510">
@@ -9571,7 +9571,7 @@
         <v>2</v>
       </c>
       <c r="D512">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="513">
@@ -9679,7 +9679,7 @@
         <v>2</v>
       </c>
       <c r="D518">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="519">
@@ -9769,7 +9769,7 @@
         <v>2</v>
       </c>
       <c r="D523">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="524">
@@ -9787,7 +9787,7 @@
         <v>2</v>
       </c>
       <c r="D524">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="525">
@@ -9823,7 +9823,7 @@
         <v>2</v>
       </c>
       <c r="D526">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="527">
@@ -9859,7 +9859,7 @@
         <v>2</v>
       </c>
       <c r="D528">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="529">
@@ -9931,7 +9931,7 @@
         <v>2</v>
       </c>
       <c r="D532">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="533">
@@ -10021,7 +10021,7 @@
         <v>2</v>
       </c>
       <c r="D537">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="538">
@@ -10183,7 +10183,7 @@
         <v>2</v>
       </c>
       <c r="D546">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="547">
@@ -10291,7 +10291,7 @@
         <v>2</v>
       </c>
       <c r="D552">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="553">
@@ -10327,7 +10327,7 @@
         <v>2</v>
       </c>
       <c r="D554">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="555">
@@ -10435,7 +10435,7 @@
         <v>21</v>
       </c>
       <c r="D560">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="561">
@@ -10507,7 +10507,7 @@
         <v>2</v>
       </c>
       <c r="D564">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="565">
@@ -10795,7 +10795,7 @@
         <v>2</v>
       </c>
       <c r="D580">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="581">
@@ -10993,7 +10993,7 @@
         <v>2</v>
       </c>
       <c r="D591">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="592">
@@ -11101,7 +11101,7 @@
         <v>2</v>
       </c>
       <c r="D597">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="598">
@@ -11371,7 +11371,7 @@
         <v>2</v>
       </c>
       <c r="D612">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="613">
@@ -11443,7 +11443,7 @@
         <v>2</v>
       </c>
       <c r="D616">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="617">
@@ -11731,7 +11731,7 @@
         <v>2</v>
       </c>
       <c r="D632">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="633">
@@ -11749,7 +11749,7 @@
         <v>2</v>
       </c>
       <c r="D633">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="634">
@@ -11839,7 +11839,7 @@
         <v>21</v>
       </c>
       <c r="D638">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="639">
@@ -11875,7 +11875,7 @@
         <v>21</v>
       </c>
       <c r="D640">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="641">
@@ -12235,7 +12235,7 @@
         <v>2</v>
       </c>
       <c r="D660">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="661">
@@ -12325,7 +12325,7 @@
         <v>2</v>
       </c>
       <c r="D665">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="666">
@@ -12649,7 +12649,7 @@
         <v>2</v>
       </c>
       <c r="D683">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="684">
@@ -12919,7 +12919,7 @@
         <v>2</v>
       </c>
       <c r="D698">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="699">
@@ -12937,7 +12937,7 @@
         <v>2</v>
       </c>
       <c r="D699">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="700">
@@ -13009,7 +13009,7 @@
         <v>2</v>
       </c>
       <c r="D703">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="704">
@@ -13063,7 +13063,7 @@
         <v>2</v>
       </c>
       <c r="D706">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="707">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C707">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C709">
@@ -13207,7 +13207,7 @@
         <v>2</v>
       </c>
       <c r="D714">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="715">
@@ -13315,7 +13315,7 @@
         <v>2</v>
       </c>
       <c r="D720">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="721">
@@ -13531,7 +13531,7 @@
         <v>2</v>
       </c>
       <c r="D732">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="733">
@@ -13729,7 +13729,7 @@
         <v>2</v>
       </c>
       <c r="D743">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="744">
@@ -13765,7 +13765,7 @@
         <v>2</v>
       </c>
       <c r="D745">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="746">
@@ -13981,7 +13981,7 @@
         <v>2</v>
       </c>
       <c r="D757">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="758">
@@ -13999,7 +13999,7 @@
         <v>2</v>
       </c>
       <c r="D758">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="759">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C759">
@@ -14161,7 +14161,7 @@
         <v>2</v>
       </c>
       <c r="D767">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="768">
@@ -14197,7 +14197,7 @@
         <v>2</v>
       </c>
       <c r="D769">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="770">
@@ -14215,7 +14215,7 @@
         <v>2</v>
       </c>
       <c r="D770">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="771">
@@ -14251,7 +14251,7 @@
         <v>2</v>
       </c>
       <c r="D772">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="773">
@@ -14287,7 +14287,7 @@
         <v>2</v>
       </c>
       <c r="D774">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="775">
@@ -14449,7 +14449,7 @@
         <v>2</v>
       </c>
       <c r="D783">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="784">
@@ -14629,7 +14629,7 @@
         <v>2</v>
       </c>
       <c r="D793">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="794">
@@ -14791,7 +14791,7 @@
         <v>2</v>
       </c>
       <c r="D802">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="803">
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="D806">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="807">
@@ -14953,7 +14953,7 @@
         <v>2</v>
       </c>
       <c r="D811">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="812">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C817">
@@ -15133,7 +15133,7 @@
         <v>2</v>
       </c>
       <c r="D821">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="822">
@@ -15493,7 +15493,7 @@
         <v>2</v>
       </c>
       <c r="D841">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="842">
@@ -15547,7 +15547,7 @@
         <v>2</v>
       </c>
       <c r="D844">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="845">
@@ -15565,7 +15565,7 @@
         <v>2</v>
       </c>
       <c r="D845">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="846">
@@ -15619,7 +15619,7 @@
         <v>2</v>
       </c>
       <c r="D848">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="849">
@@ -15637,7 +15637,7 @@
         <v>2</v>
       </c>
       <c r="D849">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="850">
@@ -15691,7 +15691,7 @@
         <v>2</v>
       </c>
       <c r="D852">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="853">
@@ -15781,7 +15781,7 @@
         <v>2</v>
       </c>
       <c r="D857">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="858">
@@ -15871,7 +15871,7 @@
         <v>2</v>
       </c>
       <c r="D862">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="863">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C869">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C870">
@@ -16069,7 +16069,7 @@
         <v>2</v>
       </c>
       <c r="D873">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="874">
@@ -16141,7 +16141,7 @@
         <v>2</v>
       </c>
       <c r="D877">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="878">
@@ -16177,7 +16177,7 @@
         <v>2</v>
       </c>
       <c r="D879">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="880">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C880">
@@ -16483,7 +16483,7 @@
         <v>2</v>
       </c>
       <c r="D896">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="897">
@@ -16573,7 +16573,7 @@
         <v>2</v>
       </c>
       <c r="D901">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="902">
@@ -16699,7 +16699,7 @@
         <v>2</v>
       </c>
       <c r="D908">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="909">
@@ -16753,7 +16753,7 @@
         <v>2</v>
       </c>
       <c r="D911">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="912">
@@ -16807,7 +16807,7 @@
         <v>2</v>
       </c>
       <c r="D914">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="915">
@@ -16987,7 +16987,7 @@
         <v>2</v>
       </c>
       <c r="D924">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="925">
@@ -17005,7 +17005,7 @@
         <v>2</v>
       </c>
       <c r="D925">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="926">
@@ -17077,7 +17077,7 @@
         <v>2</v>
       </c>
       <c r="D929">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="930">
@@ -17149,7 +17149,7 @@
         <v>2</v>
       </c>
       <c r="D933">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="934">
@@ -17365,7 +17365,7 @@
         <v>2</v>
       </c>
       <c r="D945">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="946">
@@ -17545,7 +17545,7 @@
         <v>2</v>
       </c>
       <c r="D955">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="956">
@@ -17563,7 +17563,7 @@
         <v>2</v>
       </c>
       <c r="D956">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="957">
@@ -17707,7 +17707,7 @@
         <v>2</v>
       </c>
       <c r="D964">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="965">
@@ -17887,7 +17887,7 @@
         <v>2</v>
       </c>
       <c r="D974">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="975">
@@ -18031,7 +18031,7 @@
         <v>2</v>
       </c>
       <c r="D982">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="983">
@@ -18157,7 +18157,7 @@
         <v>2</v>
       </c>
       <c r="D989">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="990">
@@ -18175,7 +18175,7 @@
         <v>21</v>
       </c>
       <c r="D990">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="991">
@@ -18247,7 +18247,7 @@
         <v>2</v>
       </c>
       <c r="D994">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="995">
@@ -18355,7 +18355,7 @@
         <v>2</v>
       </c>
       <c r="D1000">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1001">
@@ -18373,7 +18373,7 @@
         <v>2</v>
       </c>
       <c r="D1001">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1002">
@@ -18391,7 +18391,7 @@
         <v>2</v>
       </c>
       <c r="D1002">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1003">
@@ -18445,7 +18445,7 @@
         <v>2</v>
       </c>
       <c r="D1005">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1006">
@@ -18535,7 +18535,7 @@
         <v>21</v>
       </c>
       <c r="D1010">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="1011">
@@ -18589,7 +18589,7 @@
         <v>2</v>
       </c>
       <c r="D1013">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1014">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C1014">
@@ -18643,7 +18643,7 @@
         <v>2</v>
       </c>
       <c r="D1016">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1017">
@@ -18679,7 +18679,7 @@
         <v>2</v>
       </c>
       <c r="D1018">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1019">
@@ -18841,7 +18841,7 @@
         <v>2</v>
       </c>
       <c r="D1027">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1028">
@@ -18949,7 +18949,7 @@
         <v>2</v>
       </c>
       <c r="D1033">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1034">
@@ -18967,7 +18967,7 @@
         <v>2</v>
       </c>
       <c r="D1034">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1035">
@@ -19147,7 +19147,7 @@
         <v>2</v>
       </c>
       <c r="D1044">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1045">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C1049">
@@ -19327,7 +19327,7 @@
         <v>2</v>
       </c>
       <c r="D1054">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1055">
@@ -19417,7 +19417,7 @@
         <v>2</v>
       </c>
       <c r="D1059">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1060">
@@ -19759,7 +19759,7 @@
         <v>2</v>
       </c>
       <c r="D1078">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1079">
@@ -19867,7 +19867,7 @@
         <v>2</v>
       </c>
       <c r="D1084">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1085">
@@ -19921,7 +19921,7 @@
         <v>2</v>
       </c>
       <c r="D1087">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1088">
@@ -19975,7 +19975,7 @@
         <v>2</v>
       </c>
       <c r="D1090">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1091">
@@ -20011,7 +20011,7 @@
         <v>2</v>
       </c>
       <c r="D1092">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1093">
@@ -20029,7 +20029,7 @@
         <v>21</v>
       </c>
       <c r="D1093">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="1094">
@@ -20119,7 +20119,7 @@
         <v>2</v>
       </c>
       <c r="D1098">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1099">
@@ -20155,7 +20155,7 @@
         <v>2</v>
       </c>
       <c r="D1100">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1101">
@@ -20173,7 +20173,7 @@
         <v>2</v>
       </c>
       <c r="D1101">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1102">
@@ -20209,7 +20209,7 @@
         <v>2</v>
       </c>
       <c r="D1103">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1104">
@@ -20245,7 +20245,7 @@
         <v>2</v>
       </c>
       <c r="D1105">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1106">
@@ -20281,7 +20281,7 @@
         <v>2</v>
       </c>
       <c r="D1107">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1108">
@@ -20533,7 +20533,7 @@
         <v>2</v>
       </c>
       <c r="D1121">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1122">
@@ -20580,7 +20580,7 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C1124">
@@ -20641,7 +20641,7 @@
         <v>2</v>
       </c>
       <c r="D1127">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1128">
@@ -20749,7 +20749,7 @@
         <v>2</v>
       </c>
       <c r="D1133">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1134">
@@ -20821,7 +20821,7 @@
         <v>2</v>
       </c>
       <c r="D1137">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1138">
@@ -21163,7 +21163,7 @@
         <v>2</v>
       </c>
       <c r="D1156">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1157">
@@ -21343,7 +21343,7 @@
         <v>2</v>
       </c>
       <c r="D1166">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1167">
@@ -21379,7 +21379,7 @@
         <v>2</v>
       </c>
       <c r="D1168">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1169">
@@ -21865,7 +21865,7 @@
         <v>2</v>
       </c>
       <c r="D1195">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1196">
@@ -21991,7 +21991,7 @@
         <v>2</v>
       </c>
       <c r="D1202">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1203">
@@ -22081,7 +22081,7 @@
         <v>2</v>
       </c>
       <c r="D1207">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1208">
@@ -22171,7 +22171,7 @@
         <v>2</v>
       </c>
       <c r="D1212">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1213">
@@ -22225,7 +22225,7 @@
         <v>21</v>
       </c>
       <c r="D1215">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="1216">
@@ -22279,7 +22279,7 @@
         <v>2</v>
       </c>
       <c r="D1218">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1219">
@@ -22333,7 +22333,7 @@
         <v>2</v>
       </c>
       <c r="D1221">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1222">
@@ -22387,7 +22387,7 @@
         <v>2</v>
       </c>
       <c r="D1224">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1225">
@@ -22459,7 +22459,7 @@
         <v>2</v>
       </c>
       <c r="D1228">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1229">
@@ -22603,7 +22603,7 @@
         <v>2</v>
       </c>
       <c r="D1236">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1237">
@@ -22783,7 +22783,7 @@
         <v>2</v>
       </c>
       <c r="D1246">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1247">
@@ -22855,7 +22855,7 @@
         <v>2</v>
       </c>
       <c r="D1250">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1251">
@@ -22891,7 +22891,7 @@
         <v>2</v>
       </c>
       <c r="D1252">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1253">
@@ -23053,7 +23053,7 @@
         <v>2</v>
       </c>
       <c r="D1261">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1262">
@@ -23215,7 +23215,7 @@
         <v>2</v>
       </c>
       <c r="D1270">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1271">
@@ -23251,7 +23251,7 @@
         <v>2</v>
       </c>
       <c r="D1272">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1273">
@@ -23377,7 +23377,7 @@
         <v>2</v>
       </c>
       <c r="D1279">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1280">
@@ -23395,7 +23395,7 @@
         <v>21</v>
       </c>
       <c r="D1280">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="1281">
@@ -23557,7 +23557,7 @@
         <v>2</v>
       </c>
       <c r="D1289">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1290">
@@ -23593,7 +23593,7 @@
         <v>2</v>
       </c>
       <c r="D1291">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1292">
@@ -23629,7 +23629,7 @@
         <v>2</v>
       </c>
       <c r="D1293">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1294">
@@ -23683,7 +23683,7 @@
         <v>2</v>
       </c>
       <c r="D1296">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1297">
@@ -23701,7 +23701,7 @@
         <v>2</v>
       </c>
       <c r="D1297">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1298">
@@ -23917,7 +23917,7 @@
         <v>2</v>
       </c>
       <c r="D1309">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1310">
@@ -24007,7 +24007,7 @@
         <v>2</v>
       </c>
       <c r="D1314">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1315">
@@ -24061,7 +24061,7 @@
         <v>2</v>
       </c>
       <c r="D1317">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1318">
@@ -24133,7 +24133,7 @@
         <v>2</v>
       </c>
       <c r="D1321">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1322">
@@ -24313,7 +24313,7 @@
         <v>2</v>
       </c>
       <c r="D1331">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1332">
@@ -24457,7 +24457,7 @@
         <v>2</v>
       </c>
       <c r="D1339">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1340">
@@ -24511,7 +24511,7 @@
         <v>2</v>
       </c>
       <c r="D1342">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1343">
@@ -24655,7 +24655,7 @@
         <v>2</v>
       </c>
       <c r="D1350">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1351">
@@ -24673,7 +24673,7 @@
         <v>2</v>
       </c>
       <c r="D1351">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1352">
@@ -24781,7 +24781,7 @@
         <v>2</v>
       </c>
       <c r="D1357">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1358">
@@ -24799,7 +24799,7 @@
         <v>2</v>
       </c>
       <c r="D1358">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1359">
@@ -24943,7 +24943,7 @@
         <v>2</v>
       </c>
       <c r="D1366">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1367">
@@ -25195,7 +25195,7 @@
         <v>2</v>
       </c>
       <c r="D1380">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1381">
@@ -25357,7 +25357,7 @@
         <v>2</v>
       </c>
       <c r="D1389">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1390">
@@ -25591,7 +25591,7 @@
         <v>2</v>
       </c>
       <c r="D1402">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1403">
@@ -25609,7 +25609,7 @@
         <v>2</v>
       </c>
       <c r="D1403">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1404">
@@ -25987,7 +25987,7 @@
         <v>2</v>
       </c>
       <c r="D1424">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1425">
@@ -26023,7 +26023,7 @@
         <v>21</v>
       </c>
       <c r="D1426">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="1427">
@@ -26095,7 +26095,7 @@
         <v>2</v>
       </c>
       <c r="D1430">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1431">
@@ -26509,7 +26509,7 @@
         <v>21</v>
       </c>
       <c r="D1453">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="1454">
@@ -26545,7 +26545,7 @@
         <v>21</v>
       </c>
       <c r="D1455">
-        <v>0.0009679649688868403</v>
+        <v>0.0009679649688868404</v>
       </c>
     </row>
     <row r="1456">
@@ -26581,7 +26581,7 @@
         <v>2</v>
       </c>
       <c r="D1457">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1458">
@@ -26617,7 +26617,7 @@
         <v>2</v>
       </c>
       <c r="D1459">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1460">
@@ -26797,7 +26797,7 @@
         <v>2</v>
       </c>
       <c r="D1469">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1470">
@@ -27139,7 +27139,7 @@
         <v>2</v>
       </c>
       <c r="D1488">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1489">
@@ -27175,7 +27175,7 @@
         <v>2</v>
       </c>
       <c r="D1490">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1491">
@@ -27265,7 +27265,7 @@
         <v>2</v>
       </c>
       <c r="D1495">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1496">
@@ -27427,7 +27427,7 @@
         <v>2</v>
       </c>
       <c r="D1504">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1505">
@@ -27535,7 +27535,7 @@
         <v>2</v>
       </c>
       <c r="D1510">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1511">
@@ -27589,7 +27589,7 @@
         <v>2</v>
       </c>
       <c r="D1513">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1514">
@@ -27607,7 +27607,7 @@
         <v>2</v>
       </c>
       <c r="D1514">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1515">
@@ -27625,7 +27625,7 @@
         <v>2</v>
       </c>
       <c r="D1515">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1516">
@@ -27661,7 +27661,7 @@
         <v>2</v>
       </c>
       <c r="D1517">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1518">
@@ -27913,7 +27913,7 @@
         <v>2</v>
       </c>
       <c r="D1531">
-        <v>9.218713989398479E-05</v>
+        <v>9.21871398939848E-05</v>
       </c>
     </row>
     <row r="1532">
